--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92573784748</v>
+        <v>46157.93115186349</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93115186349</v>
+        <v>46157.93181613789</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93181613789</v>
+        <v>46157.93405107234</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405107234</v>
+        <v>46157.93723170403</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723170403</v>
+        <v>46158.28221009361</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221009361</v>
+        <v>46158.29698591834</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29698591834</v>
+        <v>46158.29820682058</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820682058</v>
+        <v>46158.33392026992</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392026992</v>
+        <v>46158.3686180846</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Колесник- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3686180846</v>
+        <v>46158.37292460867</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
